--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487042_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487042_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6335</v>
+        <v>4.9499</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6312</v>
+        <v>3.1886</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0022</v>
+        <v>1.7613</v>
       </c>
       <c r="G2" t="n">
         <v>3.6186</v>
@@ -610,13 +610,13 @@
         <v>1.5441</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1077</v>
+        <v>-1.5758</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5401</v>
+        <v>0.0975</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.4324</v>
+        <v>-1.6733</v>
       </c>
       <c r="V2" t="n">
         <v>1.5561</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. KARATZAS LACABEX</t>
+          <t>G. HUESO GUTIERREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1746</v>
+        <v>2.8893</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2741</v>
+        <v>1.2913</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9006</v>
+        <v>1.5981</v>
       </c>
       <c r="G3" t="n">
-        <v>6.4584</v>
+        <v>6.938</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2024</v>
+        <v>2.3226</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2559</v>
+        <v>4.6154</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2749</v>
+        <v>5.8362</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8008</v>
+        <v>2.0026</v>
       </c>
       <c r="L3" t="n">
-        <v>2.4741</v>
+        <v>3.8336</v>
       </c>
       <c r="M3" t="n">
-        <v>2.1835</v>
+        <v>1.1019</v>
       </c>
       <c r="N3" t="n">
-        <v>1.4016</v>
+        <v>0.32</v>
       </c>
       <c r="O3" t="n">
         <v>0.7818000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.386</v>
+        <v>-3.2811</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9301</v>
+        <v>-4.0532</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5441</v>
+        <v>0.772</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.6698</v>
+        <v>-1.4238</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0708</v>
+        <v>-0.4918</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.599</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.228</v>
+        <v>0.6562</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.228</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. HUESO GUTIERREZ</t>
+          <t>A. KARATZAS LACABEX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1081</v>
+        <v>2.5008</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8312</v>
+        <v>1.7341</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2769</v>
+        <v>0.7667</v>
       </c>
       <c r="G4" t="n">
-        <v>6.938</v>
+        <v>6.4584</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3226</v>
+        <v>3.2024</v>
       </c>
       <c r="I4" t="n">
-        <v>4.6154</v>
+        <v>3.2559</v>
       </c>
       <c r="J4" t="n">
-        <v>5.8362</v>
+        <v>4.2749</v>
       </c>
       <c r="K4" t="n">
-        <v>2.0026</v>
+        <v>1.8008</v>
       </c>
       <c r="L4" t="n">
-        <v>3.8336</v>
+        <v>2.4741</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1019</v>
+        <v>2.1835</v>
       </c>
       <c r="N4" t="n">
-        <v>0.32</v>
+        <v>1.4016</v>
       </c>
       <c r="O4" t="n">
         <v>0.7818000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.2811</v>
+        <v>-0.386</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.0532</v>
+        <v>-1.9301</v>
       </c>
       <c r="R4" t="n">
-        <v>0.772</v>
+        <v>1.5441</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.2051</v>
+        <v>-2.3436</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9518</v>
+        <v>-0.6107</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.2533</v>
+        <v>-1.7328</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6562</v>
+        <v>-1.228</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6562</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5866</v>
+        <v>1.6322</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.1161</v>
+        <v>-2.8564</v>
       </c>
       <c r="F5" t="n">
-        <v>4.7027</v>
+        <v>4.4885</v>
       </c>
       <c r="G5" t="n">
         <v>1.8269</v>
@@ -844,13 +844,13 @@
         <v>2.1231</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6842</v>
+        <v>-1.6386</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0708</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6133999999999999</v>
+        <v>-0.8276</v>
       </c>
       <c r="V5" t="n">
         <v>0.2859</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. JUSTO ANTOLIN</t>
+          <t>A. GUTIEZ SALGADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2719</v>
+        <v>1.4712</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3346</v>
+        <v>-1.1902</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.06270000000000001</v>
+        <v>2.6614</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3475</v>
+        <v>1.9648</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7046</v>
+        <v>2.3103</v>
       </c>
       <c r="I6" t="n">
-        <v>4.0521</v>
+        <v>-0.3456</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4665</v>
+        <v>-0.7522</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.6509</v>
+        <v>1.0557</v>
       </c>
       <c r="L6" t="n">
-        <v>3.1174</v>
+        <v>-1.8079</v>
       </c>
       <c r="M6" t="n">
-        <v>0.881</v>
+        <v>2.717</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0537</v>
+        <v>1.2547</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9346</v>
+        <v>1.4623</v>
       </c>
       <c r="P6" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.965</v>
+      </c>
+      <c r="R6" t="n">
         <v>1.3511</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-0.193</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.5441</v>
-      </c>
       <c r="S6" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-1.7794</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2247</v>
+        <v>-0.3728</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6458</v>
+        <v>-1.4066</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.5561</v>
+        <v>0.8999</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2859</v>
+        <v>0.8999</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.842</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GUTIEZ SALGADO</t>
+          <t>A. JUSTO ANTOLIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6304999999999999</v>
+        <v>1.2184</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7097</v>
+        <v>1.0937</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3402</v>
+        <v>0.1247</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9648</v>
+        <v>2.3475</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3103</v>
+        <v>-1.7046</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3456</v>
+        <v>4.0521</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7522</v>
+        <v>1.4665</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0557</v>
+        <v>-1.6509</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.8079</v>
+        <v>3.1174</v>
       </c>
       <c r="M7" t="n">
-        <v>2.717</v>
+        <v>0.881</v>
       </c>
       <c r="N7" t="n">
-        <v>1.2547</v>
+        <v>-0.0537</v>
       </c>
       <c r="O7" t="n">
-        <v>1.4623</v>
+        <v>0.9346</v>
       </c>
       <c r="P7" t="n">
-        <v>0.386</v>
+        <v>1.3511</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.965</v>
+        <v>-0.193</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3511</v>
+        <v>1.5441</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.6202</v>
+        <v>-0.9241</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8923</v>
+        <v>-0.4656</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.7279</v>
+        <v>-0.4584</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8999</v>
+        <v>-1.5561</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8999</v>
+        <v>0.2859</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0892</v>
+        <v>0.1974</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5818</v>
+        <v>-1.3221</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4927</v>
+        <v>1.5194</v>
       </c>
       <c r="G8" t="n">
         <v>3.5155</v>
@@ -1078,13 +1078,13 @@
         <v>1.5441</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.7325</v>
+        <v>-1.4459</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8328</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8996</v>
+        <v>-0.8729</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3281</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5612</v>
+        <v>-0.3808</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1105</v>
+        <v>-1.0103</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5492</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>0.8103</v>
@@ -1156,13 +1156,13 @@
         <v>0.772</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1785</v>
+        <v>-0.9981</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5949</v>
+        <v>-0.4947</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5837</v>
+        <v>-0.5034</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1564</v>
+        <v>-1.3646</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4967</v>
+        <v>-0.4372</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6597</v>
+        <v>-0.9274</v>
       </c>
       <c r="G10" t="n">
         <v>1.5276</v>
@@ -1234,13 +1234,13 @@
         <v>1.158</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7998</v>
+        <v>-1.008</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4032</v>
+        <v>-0.3437</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3966</v>
+        <v>-0.6643</v>
       </c>
       <c r="V10" t="n">
         <v>-1.8842</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.564</v>
+        <v>-1.4847</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8477</v>
+        <v>-3.688</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2837</v>
+        <v>2.2033</v>
       </c>
       <c r="G11" t="n">
         <v>-1.9124</v>
@@ -1312,13 +1312,13 @@
         <v>1.158</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8097</v>
+        <v>-0.7304</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7139</v>
+        <v>-0.5542</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0959</v>
+        <v>-0.1762</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>11.0344</v>
+        <v>11.6291</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.791400000000001</v>
+        <v>-3.1965</v>
       </c>
       <c r="F12" t="n">
-        <v>14.8258</v>
+        <v>14.8255</v>
       </c>
       <c r="G12" t="n">
         <v>27.0952</v>
@@ -1390,13 +1390,13 @@
         <v>13.5106</v>
       </c>
       <c r="S12" t="n">
-        <v>-14.4626</v>
+        <v>-13.8677</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.215099999999999</v>
+        <v>-4.6201</v>
       </c>
       <c r="U12" t="n">
-        <v>-9.247599999999998</v>
+        <v>-9.2475</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5983</v>
@@ -1405,13 +1405,13 @@
         <v>4.129</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.7274</v>
+        <v>-5.727400000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. DIAGNE</t>
+          <t>C. POLANCO MERINO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.3796</v>
+        <v>1.8379</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0955</v>
+        <v>0.0746</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2841</v>
+        <v>1.7633</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.9508</v>
+        <v>0.5139</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.5399</v>
+        <v>0.5268</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.4109</v>
+        <v>-0.0129</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.1957</v>
+        <v>0.1397</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.3178</v>
+        <v>0.1397</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1221</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.7552</v>
+        <v>0.3743</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2222</v>
+        <v>0.3871</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.533</v>
+        <v>-0.0129</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.772</v>
+        <v>1.3511</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.4741</v>
+        <v>-0.193</v>
       </c>
       <c r="R13" t="n">
-        <v>2.7021</v>
+        <v>1.5441</v>
       </c>
       <c r="S13" t="n">
-        <v>5.5609</v>
+        <v>0.5447</v>
       </c>
       <c r="T13" t="n">
-        <v>4.2238</v>
+        <v>0.1279</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3371</v>
+        <v>0.4167</v>
       </c>
       <c r="V13" t="n">
-        <v>4.5415</v>
+        <v>-0.5717</v>
       </c>
       <c r="W13" t="n">
-        <v>4.5415</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. ALLAS MENESES</t>
+          <t>M. DIAGNE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2985</v>
+        <v>1.2826</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4013</v>
+        <v>0.293</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6998</v>
+        <v>0.9896</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.5353</v>
+        <v>-5.9508</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6985</v>
+        <v>-4.5399</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.2338</v>
+        <v>-1.4109</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0309</v>
+        <v>-3.1957</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0309</v>
+        <v>-3.3178</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.1221</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5662</v>
+        <v>-2.7552</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6676</v>
+        <v>-1.2222</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.2338</v>
+        <v>-1.533</v>
       </c>
       <c r="P14" t="n">
-        <v>1.158</v>
+        <v>-0.772</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.386</v>
+        <v>-3.4741</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5441</v>
+        <v>2.7021</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3054</v>
+        <v>3.4639</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0462</v>
+        <v>2.4213</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3516</v>
+        <v>1.0427</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3704</v>
+        <v>4.5415</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>4.5415</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. DE LA CRUZ MARTINEZ</t>
+          <t>D. ALLAS MENESES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9255</v>
+        <v>1.245</v>
       </c>
       <c r="E15" t="n">
-        <v>2.188</v>
+        <v>-0.4013</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2625</v>
+        <v>1.6463</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.0612</v>
+        <v>-0.5353</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.304</v>
+        <v>0.6985</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2428</v>
+        <v>-1.2338</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0543</v>
+        <v>0.0309</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6212</v>
+        <v>0.0309</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6755</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.1155</v>
+        <v>-0.5662</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.6828</v>
+        <v>0.6676</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4327</v>
+        <v>-1.2338</v>
       </c>
       <c r="P15" t="n">
-        <v>0.772</v>
+        <v>1.158</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.193</v>
+        <v>-0.386</v>
       </c>
       <c r="R15" t="n">
-        <v>0.965</v>
+        <v>1.5441</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5005</v>
+        <v>0.2518</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3267</v>
+        <v>-0.0462</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1738</v>
+        <v>0.2981</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2859</v>
+        <v>0.3704</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2859</v>
+        <v>0.3704</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ALLAS MENESES</t>
+          <t>G. DE LA CRUZ MARTINEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8925</v>
+        <v>0.6052</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0218</v>
+        <v>1.7874</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1293</v>
+        <v>-1.1822</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.1119</v>
+        <v>-2.0612</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8591</v>
+        <v>-2.304</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2527</v>
+        <v>0.2428</v>
       </c>
       <c r="J16" t="n">
-        <v>0.483</v>
+        <v>0.0543</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7036</v>
+        <v>-0.6212</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.2206</v>
+        <v>0.6755</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5948</v>
+        <v>-2.1155</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.5627</v>
+        <v>-1.6828</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0321</v>
+        <v>-0.4327</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0.772</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.158</v>
+        <v>-0.193</v>
       </c>
       <c r="R16" t="n">
-        <v>1.158</v>
+        <v>0.965</v>
       </c>
       <c r="S16" t="n">
-        <v>3.8463</v>
+        <v>2.1803</v>
       </c>
       <c r="T16" t="n">
-        <v>2.6969</v>
+        <v>1.9262</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1494</v>
+        <v>0.2541</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.842</v>
+        <v>-0.2859</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.842</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. POLANCO MERINO</t>
+          <t>A. ALLAS MENESES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6422</v>
+        <v>0.0507</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8267</v>
+        <v>1.421</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4689</v>
+        <v>-1.3702</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5139</v>
+        <v>-1.1119</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5268</v>
+        <v>-0.8591</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0129</v>
+        <v>-0.2527</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1397</v>
+        <v>0.483</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1397</v>
+        <v>0.7036</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.2206</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3743</v>
+        <v>-1.5948</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3871</v>
+        <v>-1.5627</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0129</v>
+        <v>-0.0321</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3511</v>
+        <v>-0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.193</v>
+        <v>-1.158</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5441</v>
+        <v>1.158</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6511</v>
+        <v>3.0045</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7733</v>
+        <v>2.096</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1223</v>
+        <v>0.9085</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5717</v>
+        <v>-1.842</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5717</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2435</v>
+        <v>-0.0968</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9443</v>
+        <v>-0.7441</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7008</v>
+        <v>0.6473</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5198</v>
@@ -1858,13 +1858,13 @@
         <v>0.579</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3027</v>
+        <v>-0.156</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2974</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0053</v>
+        <v>-0.0588</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4449</v>
+        <v>-0.7454</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.203</v>
+        <v>-1.5034</v>
       </c>
       <c r="F19" t="n">
         <v>0.758</v>
@@ -1936,10 +1936,10 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5936</v>
+        <v>0.2931</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4297</v>
+        <v>0.1292</v>
       </c>
       <c r="U19" t="n">
         <v>0.1639</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5798</v>
+        <v>-3.5133</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.9681</v>
+        <v>-3.7678</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3883</v>
+        <v>0.2545</v>
       </c>
       <c r="G20" t="n">
         <v>-4.3934</v>
@@ -2014,13 +2014,13 @@
         <v>1.7371</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3504</v>
+        <v>1.4168</v>
       </c>
       <c r="T20" t="n">
-        <v>0.16</v>
+        <v>0.3603</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1904</v>
+        <v>1.0566</v>
       </c>
       <c r="V20" t="n">
         <v>0.0422</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.0242</v>
+        <v>-3.8017</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.4378</v>
+        <v>-3.5365</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5864</v>
+        <v>-0.2651</v>
       </c>
       <c r="G21" t="n">
         <v>-4.806</v>
@@ -2092,13 +2092,13 @@
         <v>1.158</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1679</v>
+        <v>1.3904</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1309</v>
+        <v>1.0322</v>
       </c>
       <c r="U21" t="n">
-        <v>0.037</v>
+        <v>0.3582</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.8802</v>
+        <v>-7.8986</v>
       </c>
       <c r="E22" t="n">
-        <v>-9.3497</v>
+        <v>-8.448399999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4696</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>-8.1572</v>
@@ -2170,13 +2170,13 @@
         <v>2.1231</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0913</v>
+        <v>2.0729</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3966</v>
+        <v>1.2979</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6947</v>
+        <v>0.775</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6562</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-11.0343</v>
+        <v>-11.0344</v>
       </c>
       <c r="E23" t="n">
-        <v>-14.8256</v>
+        <v>-14.8255</v>
       </c>
       <c r="F23" t="n">
-        <v>3.791300000000001</v>
+        <v>3.791400000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-27.0952</v>
@@ -2239,7 +2239,7 @@
         <v>-6.3299</v>
       </c>
       <c r="P23" t="n">
-        <v>9.999999999976694e-05</v>
+        <v>0.000100000000000211</v>
       </c>
       <c r="Q23" t="n">
         <v>-13.5104</v>
@@ -2248,13 +2248,13 @@
         <v>13.5105</v>
       </c>
       <c r="S23" t="n">
-        <v>14.4625</v>
+        <v>14.4624</v>
       </c>
       <c r="T23" t="n">
-        <v>9.2477</v>
+        <v>9.2476</v>
       </c>
       <c r="U23" t="n">
-        <v>5.2149</v>
+        <v>5.215</v>
       </c>
       <c r="V23" t="n">
         <v>1.5983</v>
